--- a/Updated Project3.xlsx
+++ b/Updated Project3.xlsx
@@ -413,7 +413,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -482,11 +482,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -512,6 +596,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -521,59 +624,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,62 +974,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="36"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -965,196 +1067,196 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
       <c r="G7" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="10"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="11" t="s">
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="18" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
       <c r="G9" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="13" t="s">
         <v>112</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="24"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="13" t="s">
         <v>114</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="24"/>
     </row>
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="13" t="s">
         <v>83</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="10"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="11" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="I12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
       <c r="G13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="10"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="11" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="18" t="s">
         <v>101</v>
       </c>
       <c r="E14" s="7" t="s">
@@ -1166,10 +1268,10 @@
       <c r="G14" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="I14" s="13" t="s">
         <v>36</v>
       </c>
       <c r="J14" s="7" t="s">
@@ -1180,10 +1282,10 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="7" t="s">
         <v>27</v>
       </c>
@@ -1193,10 +1295,10 @@
       <c r="G15" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="30" t="s">
+      <c r="I15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="J15" s="7" t="s">
@@ -1207,10 +1309,10 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="7" t="s">
         <v>31</v>
       </c>
@@ -1220,10 +1322,10 @@
       <c r="G16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="30" t="s">
+      <c r="H16" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="I16" s="13" t="s">
         <v>45</v>
       </c>
       <c r="J16" s="7" t="s">
@@ -1234,10 +1336,10 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
       <c r="E17" s="7" t="s">
         <v>33</v>
       </c>
@@ -1247,10 +1349,10 @@
       <c r="G17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="30" t="s">
+      <c r="I17" s="13" t="s">
         <v>102</v>
       </c>
       <c r="J17" s="7" t="s">
@@ -1261,12 +1363,12 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="11" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="18" t="s">
         <v>50</v>
       </c>
       <c r="E18" s="7" t="s">
@@ -1278,10 +1380,10 @@
       <c r="G18" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="30" t="s">
+      <c r="H18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="I18" s="13" t="s">
         <v>53</v>
       </c>
       <c r="J18" s="7" t="s">
@@ -1292,10 +1394,10 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
       <c r="E19" s="7" t="s">
         <v>43</v>
       </c>
@@ -1305,10 +1407,10 @@
       <c r="G19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="30" t="s">
+      <c r="I19" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J19" s="7" t="s">
@@ -1319,290 +1421,341 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="11" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="18" t="s">
         <v>60</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="27" t="s">
+      <c r="H20" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
       <c r="G21" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="10"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="17"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="11" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="18" t="s">
         <v>64</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="H22" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="I22" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="10"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="11" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="18" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="27" t="s">
+      <c r="H24" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
       <c r="G25" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="10"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="17"/>
     </row>
     <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="11" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="18" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="27" t="s">
+      <c r="H26" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="I26" s="27" t="s">
+      <c r="I26" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
       <c r="G27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="10"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="11" t="s">
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="18" t="s">
         <v>75</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="I28" s="27" t="s">
+      <c r="I28" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="17"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="24"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
       <c r="G30" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="17"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="24"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
       <c r="G31" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="17"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="24"/>
     </row>
     <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
       <c r="G32" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="17"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="24"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
+      <c r="A33" s="27"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
       <c r="G33" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="10"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="17"/>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="A6:A33"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B6:B33"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
@@ -1619,57 +1772,6 @@
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="K8:K11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="B6:B33"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="A6:A33"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
